--- a/output/casestudy_20260822.xlsx
+++ b/output/casestudy_20260822.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>12.93968820001464</v>
+        <v>12.88186490000226</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.67373330006376</v>
+        <v>10.89963020000141</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>10.96674629999325</v>
+        <v>11.20561870001256</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.17597360000946</v>
+        <v>11.35039090004284</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.21755790000316</v>
+        <v>11.48497589991894</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>11.400584399933</v>
+        <v>11.56699560000561</v>
       </c>
     </row>
   </sheetData>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.7 초</t>
+          <t>10.9 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.0 초</t>
+          <t>11.2 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.2 초</t>
+          <t>11.4 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.2 초</t>
+          <t>11.5 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11.4 초</t>
+          <t>11.6 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>70.3 초</t>
+          <t>71.5 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260822.xlsx
+++ b/output/casestudy_20260822.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>12.88186490000226</v>
+        <v>11.73598849994596</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>10.89963020000141</v>
+        <v>11.65384709998034</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>11.20561870001256</v>
+        <v>12.13160760002211</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>11.35039090004284</v>
+        <v>12.45008919993415</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>11.48497589991894</v>
+        <v>12.57712060003541</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>11.56699560000561</v>
+        <v>12.65964130009525</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12.9 초</t>
+          <t>11.7 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10.9 초</t>
+          <t>11.7 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>11.2 초</t>
+          <t>12.1 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.4 초</t>
+          <t>12.5 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11.5 초</t>
+          <t>12.6 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11.6 초</t>
+          <t>12.7 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>71.5 초</t>
+          <t>75.1 초</t>
         </is>
       </c>
     </row>

--- a/output/casestudy_20260822.xlsx
+++ b/output/casestudy_20260822.xlsx
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>11.73598849994596</v>
+        <v>12.33004539995454</v>
       </c>
     </row>
     <row r="3">
@@ -596,7 +596,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>11.65384709998034</v>
+        <v>12.36227790010162</v>
       </c>
     </row>
     <row r="4">
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>12.13160760002211</v>
+        <v>12.77821359992959</v>
       </c>
     </row>
     <row r="5">
@@ -700,7 +700,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>12.45008919993415</v>
+        <v>13.14582430000883</v>
       </c>
     </row>
     <row r="6">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>12.57712060003541</v>
+        <v>13.72108309995383</v>
       </c>
     </row>
     <row r="7">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>12.65964130009525</v>
+        <v>13.74982220004313</v>
       </c>
     </row>
   </sheetData>
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11.7 초</t>
+          <t>12.3 초</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11.7 초</t>
+          <t>12.4 초</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12.1 초</t>
+          <t>12.8 초</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12.5 초</t>
+          <t>13.1 초</t>
         </is>
       </c>
     </row>
@@ -7585,7 +7585,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12.6 초</t>
+          <t>13.7 초</t>
         </is>
       </c>
     </row>
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12.7 초</t>
+          <t>13.7 초</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7609,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>75.1 초</t>
+          <t>80.2 초</t>
         </is>
       </c>
     </row>
